--- a/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -780,13 +768,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -798,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1090,13 +1078,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1108,7 +1096,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1341,7 +1329,7 @@
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
         <v>15</v>
@@ -1353,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
         <v>30</v>
@@ -1648,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>48</v>
@@ -1663,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -1710,25 +1698,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>11</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1772,7 +1760,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
         <v>85</v>
@@ -1787,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L22" t="n">
         <v>20</v>
@@ -2206,7 +2194,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
         <v>12</v>
@@ -2221,10 +2209,10 @@
         <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2268,10 +2256,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2286,7 +2274,7 @@
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L30" t="n">
         <v>8</v>
@@ -2581,7 +2569,7 @@
         <v>184</v>
       </c>
       <c r="F35" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2593,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
         <v>196</v>

--- a/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -1096,7 +1096,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>38</v>
@@ -1701,7 +1701,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>10</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F35" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>13</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>38</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
         <v>48</v>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -1701,7 +1701,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" t="n">
         <v>18</v>
@@ -1778,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>124</v>
       </c>
       <c r="F23" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>125</v>
@@ -2026,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>87</v>
       </c>
       <c r="F30" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2271,13 +2271,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F35" t="n">
         <v>75</v>
@@ -2581,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
